--- a/results/Int Task Remove ACC -0.5/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001015384274395368</v>
+        <v>0.0004753336959156105</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.002529513816789408</v>
+        <v>0.000175378687765584</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0002715950096516761</v>
+        <v>0.00136949177723508</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005607412267339908</v>
+        <v>0.0008265068779640805</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.002808606005865462</v>
+        <v>0.002113910178295415</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.002566443467784945</v>
+        <v>-0.0006939371406487074</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.888877520594081e-05</v>
+        <v>2.319878257813768e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0008774459064118079</v>
+        <v>-3.702733129505409e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008090193253076458</v>
+        <v>0.01222452363302757</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01167532666027146</v>
+        <v>0.01323788889532635</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.451413693150501e-05</v>
+        <v>0.0003315860657068104</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.001756039453817</v>
+        <v>-0.0001216658259415516</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0008152409943753111</v>
+        <v>0.00100204598157681</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005561377578048448</v>
+        <v>0.009332369798737774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001643486333747947</v>
+        <v>0.005335592596049726</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.002530722089678671</v>
+        <v>-0.0005889640989197885</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001388958759962004</v>
+        <v>0.0005918735772465723</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.001120490755058916</v>
+        <v>-0.0006126913880695594</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0005898322323368032</v>
+        <v>0.0001452758674877763</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.300293287025301e-05</v>
+        <v>6.110023692049713e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0004561605638804578</v>
+        <v>-0.0009510123760557234</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.001086657056323617</v>
+        <v>-0.0005259873839241603</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0005274715284848231</v>
+        <v>0.0007205267438670259</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.577501724528308e-05</v>
+        <v>0.000713490511780367</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007351989232888378</v>
+        <v>0.001207639652484377</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.709755070147041e-05</v>
+        <v>0.000359281691351242</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.003304821417699971</v>
+        <v>0.002539320187947125</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.00184939672108188</v>
+        <v>-0.001505717821621782</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.001331912789696745</v>
+        <v>0.0011194583726574</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002458878098891235</v>
+        <v>-0.0001497142719888999</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.662712450099302e-05</v>
+        <v>0.000204514070355869</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0002364865303546848</v>
+        <v>0.0004068650138114982</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0002213941729957758</v>
+        <v>-0.001261896492908453</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.002582949102066124</v>
+        <v>-0.002001344464265125</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.001610572770376e-05</v>
+        <v>4.137047093761946e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0001167181950976337</v>
+        <v>0.0007423225792315958</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.002763077656151549</v>
+        <v>0.002404731254408854</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001013351127729322</v>
+        <v>-0.001260068676544522</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0001380889754677594</v>
+        <v>-0.0001622452846257705</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001167869000651193</v>
+        <v>0.001201053799253917</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.001280144286771245</v>
+        <v>-0.00121454114941532</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0005335338420587389</v>
+        <v>0.001168411300785734</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0006794825889507106</v>
+        <v>-0.002366354034723526</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.0006724442349862469</v>
+        <v>0.002541044290174493</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0002532570820121782</v>
+        <v>0.0002971044006706667</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0001491610780571948</v>
+        <v>-0.001092020461881668</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0005302247845329056</v>
+        <v>0.0003604458319368697</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0002940514878145551</v>
+        <v>0.001500243089376241</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.001658814234511275</v>
+        <v>-0.001088711071951342</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.005399193142501685</v>
+        <v>-0.005456832882168501</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.003150872326684416</v>
+        <v>-0.004024540998466082</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0002248256752542155</v>
+        <v>-0.0001606007631731132</v>
       </c>
       <c r="BD3" t="n">
-        <v>-2.310448680818978e-05</v>
+        <v>5.103851198340001e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0003794265827283317</v>
+        <v>-0.0003007224286396315</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.003997576013321391</v>
+        <v>-0.006514165885081103</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002052020036741413</v>
+        <v>-0.0009181269738768238</v>
       </c>
       <c r="BH3" t="n">
-        <v>-2.378121284185575e-05</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.000100618869848097</v>
+        <v>0.0003100495516391056</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.0009677283194725085</v>
+        <v>-0.0001464301338034356</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002906452000396632</v>
+        <v>-0.003278552322631058</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0001480940160819777</v>
+        <v>3.88259047328754e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001836768130007265</v>
+        <v>-0.0008307468898737036</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.003884966899580076</v>
+        <v>-0.005753103857041361</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0003166920670769547</v>
+        <v>0.0003446345578878308</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.002846988854715504</v>
+        <v>0.001611000897944649</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0001341592606725906</v>
+        <v>0.0001857999365343988</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.002101538180702695</v>
+        <v>0.0028351237787846</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.001959188390739959</v>
+        <v>-0.0002702422284921024</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0002369700351722415</v>
+        <v>0.0001606315039306206</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.002157395141478532</v>
+        <v>0.005181502730911119</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0009450684700355218</v>
+        <v>0.001052710585717833</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.003355875347617286</v>
+        <v>0.002906944565991718</v>
       </c>
       <c r="BX3" t="n">
-        <v>-5.356332724901548e-05</v>
+        <v>-1.007931208585554e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0004395279543753327</v>
+        <v>0.001002122404602629</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0001991011806958076</v>
+        <v>0.000362588114953899</v>
       </c>
       <c r="CA3" t="n">
-        <v>-1.486325802615984e-05</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0001091036567404602</v>
+        <v>0.0002044836433178632</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.001364641703998089</v>
+        <v>-0.0003296803603911835</v>
       </c>
       <c r="CD3" t="n">
-        <v>-4.435638535943642e-05</v>
+        <v>-0.0003146860706322285</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0001805774783513403</v>
+        <v>0.0002929064812000504</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0006656688809151369</v>
+        <v>0.0001086379868958941</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0003411474007802064</v>
+        <v>0.002731447567377747</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002516646536921429</v>
+        <v>6.639287884399269e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0008089933498713422</v>
+        <v>-0.001247698628329323</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.000136594889377506</v>
+        <v>0.003171965733054794</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0008051073194603964</v>
+        <v>0.000870283013588119</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004606382887974776</v>
+        <v>0.003338282587426166</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007101777643463016</v>
+        <v>0.004692270712728474</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004819301060538872</v>
+        <v>0.00522773366849215</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006566176742189326</v>
+        <v>0.003476148425283579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007606911682446064</v>
+        <v>0.003469627421631904</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008002607881165101</v>
+        <v>0.004866602442180341</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003246387308798387</v>
+        <v>0.0003949031266072754</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004363082651801539</v>
+        <v>0.002362625786860262</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01163193106680436</v>
+        <v>0.01006196205731087</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01530373253718901</v>
+        <v>0.01154697838859259</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003832770870381632</v>
+        <v>0.003734001290731864</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007289085822928656</v>
+        <v>0.005316215605174568</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007967889575458154</v>
+        <v>0.004692707353126511</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0184188780529383</v>
+        <v>0.01579560174120737</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008066548369693248</v>
+        <v>0.007015913565386457</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00434795390694784</v>
+        <v>0.003493770975501432</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004765290054882137</v>
+        <v>0.003112411019136369</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003313902837006634</v>
+        <v>0.003488697250369597</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003928584483152581</v>
+        <v>0.00436164035030813</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003282204208759731</v>
+        <v>0.0004190634552718841</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007664244099306806</v>
+        <v>0.007733250548726128</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005593734032410596</v>
+        <v>0.002922198861143567</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002034269261462818</v>
+        <v>0.002120644249553551</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001798425145966187</v>
+        <v>0.0009995586100069083</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002017342816195057</v>
+        <v>0.002986345487911463</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000500838465601817</v>
+        <v>0.000637186839803084</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004780362339385808</v>
+        <v>0.002926205044423197</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008122270144706964</v>
+        <v>0.005475064259250878</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004718245685885178</v>
+        <v>0.005904116352637854</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.006628295777766679</v>
+        <v>0.004367102756422291</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006117019013720651</v>
+        <v>0.0004975643744250543</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0008198284173086409</v>
+        <v>0.0005562914328610347</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005601785200501253</v>
+        <v>0.005227215120212833</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.005383135400599987</v>
+        <v>0.003435267054523776</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0006841935806971301</v>
+        <v>0.0008002392778358976</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0009180146633601499</v>
+        <v>0.0008748818542080344</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.003444672528537726</v>
+        <v>0.003798303815451137</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004367774155756792</v>
+        <v>0.002526725777635378</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001455179339271183</v>
+        <v>0.001093130924008496</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00249587906180774</v>
+        <v>0.003117577111299782</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.003739771761092147</v>
+        <v>0.003546955542316303</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002538660143625655</v>
+        <v>0.003504409699941064</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.006874579977174242</v>
+        <v>0.006210420569833103</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.004809560016542442</v>
+        <v>0.008644892330278708</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002753466177554867</v>
+        <v>0.003868325487656256</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002956934705551115</v>
+        <v>0.002058478438058002</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.00115080642273415</v>
+        <v>0.0009288057628567876</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.00318691484724919</v>
+        <v>0.002398070045935556</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004464849239619399</v>
+        <v>0.009383555437046507</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.006946155701451201</v>
+        <v>0.0115393249064828</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006781656556320012</v>
+        <v>0.009213270983371645</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001078571573054508</v>
+        <v>0.0007691694451419262</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001227774061234061</v>
+        <v>0.0008021914750812233</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0006488774941401366</v>
+        <v>0.0007489648828412736</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01118907570915324</v>
+        <v>0.008260007052490539</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.006992740114962462</v>
+        <v>0.007859585170084241</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.520279810150981e-05</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001288425155510631</v>
+        <v>0.001319944119824891</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002307577891591263</v>
+        <v>0.003496896841255147</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.008280413797073397</v>
+        <v>0.008967541776885935</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0007048606545204593</v>
+        <v>0.0006877850192417639</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.004048747636084438</v>
+        <v>0.003986995566951418</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005953363495664389</v>
+        <v>0.01122758564142692</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.007826380482893584</v>
+        <v>0.005577713350565509</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0100857673815933</v>
+        <v>0.005597485117779518</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0004126907590439394</v>
+        <v>0.000239827957090832</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.006258878816628304</v>
+        <v>0.0071358272912901</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003373205088910464</v>
+        <v>0.002045115173111632</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002203434944124998</v>
+        <v>0.001828556693285453</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01261334237381268</v>
+        <v>0.008456097262758139</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.005608820057359595</v>
+        <v>0.003714394748682143</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.01021793934643112</v>
+        <v>0.006697649582802842</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001665753773532259</v>
+        <v>0.000224597961755927</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001064983368355531</v>
+        <v>0.0009821395261752134</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002750663198894757</v>
+        <v>0.0006822676331020865</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.700174881344362e-05</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001361771570580623</v>
+        <v>0.000918007628334016</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.004583953471497861</v>
+        <v>0.002787006747898751</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0001753933058848723</v>
+        <v>0.0005807088055424186</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001373522348851315</v>
+        <v>0.0009488114028198429</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.006857693649134636</v>
+        <v>0.003368704413136573</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004624619883720143</v>
+        <v>0.003912092094861906</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001937711733763865</v>
+        <v>0.001471598397173843</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.005422995632827217</v>
+        <v>0.002243638041074569</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.006422593653819333</v>
+        <v>0.006660011539519769</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002930543367464949</v>
+        <v>0.001591169646201812</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0061743341404358</v>
+        <v>-0.006355932203389781</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01643667586629865</v>
+        <v>-0.00767123287671233</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01047184170471841</v>
+        <v>-0.007610350076103489</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01517486662714884</v>
+        <v>-0.00621486570893196</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.02012711864406778</v>
+        <v>-0.003926940639269428</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01973365617433413</v>
+        <v>-0.005765102729224226</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0006541778174249724</v>
+        <v>-0.0005309181761399163</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01062348668280868</v>
+        <v>-0.005296610169491489</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01112102289622368</v>
+        <v>-0.003287671232876721</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.01451085340469823</v>
+        <v>-0.01187214611872146</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004726516052318686</v>
+        <v>-0.005124960455552041</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01498184019370458</v>
+        <v>-0.009079903147699731</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01719128329297819</v>
+        <v>-0.007475786924939443</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.02201778595522842</v>
+        <v>-0.01765755053507727</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01113155473781047</v>
+        <v>-0.006075874333135722</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01268524007113225</v>
+        <v>-0.00602739726027397</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01141041162227601</v>
+        <v>-0.003450363196125872</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.006164789567279283</v>
+        <v>-0.006961259079903115</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.00550847457627115</v>
+        <v>-0.005423829282750425</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0003865596193875165</v>
+        <v>-0.0008119925046845778</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01743289108299905</v>
+        <v>-0.009931608682723714</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.008180201541197474</v>
+        <v>-0.005447941888619812</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.003260225251926529</v>
+        <v>-0.003054612773835208</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.00221448908573233</v>
+        <v>-0.0007433838834373874</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.001518506801645014</v>
+        <v>-0.004319654427645747</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0009256402344954839</v>
+        <v>-0.0003568242640499264</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.007824540604623675</v>
+        <v>-0.0004756242568370483</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01959098992294017</v>
+        <v>-0.009987893462469699</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.008476585655008972</v>
+        <v>-0.009036860879904841</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01361545538178469</v>
+        <v>-0.008126341613002196</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001119854721549607</v>
+        <v>-0.0003865596193874277</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001664648910411592</v>
+        <v>-0.000308546744831828</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.007202133965619528</v>
+        <v>-0.01238883777982217</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0124777711914642</v>
+        <v>-0.00723365617433408</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0008298755186721962</v>
+        <v>-0.001397146254458925</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002115915363385434</v>
+        <v>-0.0006355932203389259</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.002027845036319598</v>
+        <v>-0.004381363776612112</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.007765263781861376</v>
+        <v>-0.005901937046004791</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002594115786143625</v>
+        <v>-0.001866497943688661</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003813559322033877</v>
+        <v>-0.004905893242826254</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.006757557794902269</v>
+        <v>-0.005519779208831699</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.006420927467300852</v>
+        <v>-0.004577883472057042</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01105022831050226</v>
+        <v>-0.01735159817351599</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.006818883060783654</v>
+        <v>-0.006628329297820779</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.004176755447941849</v>
+        <v>-0.00797564687975647</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004474885844748843</v>
+        <v>-0.00484072454715806</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0008022215365627416</v>
+        <v>-0.001070472792149835</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.007587433313574476</v>
+        <v>-0.002404870624048694</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.008050847457627108</v>
+        <v>-0.01811263318112634</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01796042617960426</v>
+        <v>-0.03318112633181125</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.02088280060882799</v>
+        <v>-0.02773211567732117</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001967520299812631</v>
+        <v>-0.001613394216133956</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001543583535108928</v>
+        <v>-0.0011972463334331</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.001634382566585946</v>
+        <v>-0.001784121320249765</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02127853881278539</v>
+        <v>-0.01993911719939118</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.0109284627092846</v>
+        <v>-0.01735159817351597</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.0002378121284185575</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003260225251926519</v>
+        <v>-0.001570835803200943</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.004538485127261538</v>
+        <v>-0.004535768645357685</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.02322678843226788</v>
+        <v>-0.02207001522070017</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.00060882800608828</v>
+        <v>-0.0008917954815694906</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.006757557794902269</v>
+        <v>-0.008127853881278535</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01205479452054794</v>
+        <v>-0.03318112633181125</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01323665535328599</v>
+        <v>-0.01021289725393394</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.02993479549496147</v>
+        <v>-0.004596651445966526</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0001898133502056254</v>
+        <v>-0.0003123048094940684</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.01867219917012453</v>
+        <v>-0.004048706240487065</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.002279825109306699</v>
+        <v>-0.002815564694716821</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.005364552459988204</v>
+        <v>-0.001856925418569255</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.02777119146413753</v>
+        <v>-0.004564315352697079</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.01633076467101369</v>
+        <v>-0.004809741248097421</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.03135743924125668</v>
+        <v>-0.003389830508474523</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.000367985280588734</v>
+        <v>-0.0002963841138114987</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.003260225251926507</v>
+        <v>6.17093489663878e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.007231772377000678</v>
+        <v>-0.001089588377723905</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.0001486325802615984</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.002904564315352698</v>
+        <v>-0.001659751037344392</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.01004742145820992</v>
+        <v>-0.006232204998418212</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.0005350772889417543</v>
+        <v>-0.001724137931034431</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003645524599881489</v>
+        <v>-0.001405371642723308</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.01926496739774752</v>
+        <v>-0.00541856925418569</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.01149970361588626</v>
+        <v>-0.002739726027397282</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.003438055720213451</v>
+        <v>-0.001248097412480986</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.01487848251333734</v>
+        <v>-0.004630481447408819</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.01656787196206289</v>
+        <v>-0.006727549467275507</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.007824540604623675</v>
+        <v>-0.002058111380145233</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001512036015793802</v>
+        <v>-0.001931769491660498</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.005991939594749576</v>
+        <v>-0.00236284699546882</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001955256910291883</v>
+        <v>-0.001509564265369132</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001240140275713142</v>
+        <v>0.000617610971762561</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.004554786663171079</v>
+        <v>0.00173042882596712</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00116436886972289</v>
+        <v>-0.004240869323326272</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0002207439163266905</v>
+        <v>-0.0001437936625227065</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002578350085849679</v>
+        <v>-0.001370318094430001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001766606393855657</v>
+        <v>0.007465359829581639</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002709411312702484</v>
+        <v>0.007513057075796389</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001488627895359004</v>
+        <v>-0.001238667948650615</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002831601871221045</v>
+        <v>-0.001874832974363644</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.00192892375123945</v>
+        <v>-0.0009715781875492463</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.004234500446030345</v>
+        <v>0.003726385257095696</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.003101418523434285</v>
+        <v>0.0007782963765345901</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.003622181081279738</v>
+        <v>-0.002468308249525264</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002572354435587707</v>
+        <v>-0.00153623399472905</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.003952867107268863</v>
+        <v>-0.002383663477127318</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.003414846314660627</v>
+        <v>-0.003886819999231753</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0003017187396532617</v>
+        <v>-3.057082283202394e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002062661296693133</v>
+        <v>-0.006938850117115666</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.005240281914147127</v>
+        <v>-0.001768442182142393</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0002693804250224613</v>
+        <v>7.278147300454617e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.001292330075267872</v>
+        <v>0.0001267481639255413</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0003322594111026339</v>
+        <v>0.0002035107415209903</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001921373668067883</v>
+        <v>-0.0002545984162828502</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.002116883712970821</v>
+        <v>3.833180006135307e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.00369813267805548</v>
+        <v>-0.004352401592368559</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.003457276442116683</v>
+        <v>-0.002404572223611723</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.006617047948240598</v>
+        <v>-0.002371548400561186</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0003255232384460349</v>
+        <v>-9.271695088803599e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0005283619079209517</v>
+        <v>7.431558866888288e-05</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.004687705348928877</v>
+        <v>-0.002851874299070634</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.00557500787580314</v>
+        <v>-0.00358836291798488</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0005285791010482294</v>
+        <v>-0.0004390592001172034</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0002045604055413291</v>
+        <v>0.0003452580484481854</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0001246493943833999</v>
+        <v>0.0002312123097505697</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002871320309305261</v>
+        <v>-0.002950826895016337</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0007160980818523676</v>
+        <v>-0.00098999263643674</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.401713920305692e-05</v>
+        <v>-0.0002150486689330849</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.004149121094212916</v>
+        <v>-0.003185458832812379</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.001210369190448726</v>
+        <v>-0.0008602988456089782</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.004116222760290577</v>
+        <v>-0.00442330098400795</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.00456780870290896</v>
+        <v>-0.003507061776993014</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001424665629851182</v>
+        <v>-0.0009834010289538316</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.002969727229043109</v>
+        <v>-0.001717971906445123</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001333728512151744</v>
+        <v>-0.0001419683598116672</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.000409310049067782</v>
+        <v>-0.0002998408615751652</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.005073358589703874</v>
+        <v>-0.004703075203304676</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.006467041544539304</v>
+        <v>-0.009372438676845354</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.004079645695397541</v>
+        <v>-0.00553047113743565</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0007623667218894737</v>
+        <v>-0.0004877099139321078</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0006598995871111819</v>
+        <v>-0.000438422432760982</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0006258653266659281</v>
+        <v>-0.0005518299441745617</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.01139263498743427</v>
+        <v>-0.01203047342933601</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.006817825753475084</v>
+        <v>-0.006367345150977852</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0003877451724048353</v>
+        <v>-0.0002687010692975889</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.003184950156649485</v>
+        <v>-0.003147790136466563</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.002616262088042834</v>
+        <v>-0.00814935794017709</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0002868598953641305</v>
+        <v>-0.0004554987370186669</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0002895823506578743</v>
+        <v>-0.002001231447298621</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.009356249123358584</v>
+        <v>-0.007051296426145312</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.002806731295656656</v>
+        <v>-0.00299073797922326</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.003340089280406686</v>
+        <v>-0.001828112557134873</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-5.206796714782857e-05</v>
+        <v>0.0001793710112887648</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.002957634715874649</v>
+        <v>-0.0028807342790833</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0004955164336830798</v>
+        <v>-0.001838291915840493</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0005562787853683971</v>
+        <v>-0.001097445244731485</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.000416162227602912</v>
+        <v>-0.0004434685158046847</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001043466319902564</v>
+        <v>-0.00113854298511808</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.002800955403175692</v>
+        <v>-0.00289856165770726</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0001114348745483662</v>
+        <v>-0.0001895637451337861</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0004926262796138309</v>
+        <v>0.0003139953642034315</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0002931070937981506</v>
+        <v>0.0002192880622731763</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003865441506384432</v>
+        <v>-6.270199617973982e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0004328762633101973</v>
+        <v>-0.001275068422087619</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0.0004347937065834528</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.000212261718957496</v>
+        <v>-0.0001511846364639164</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0004561475001559568</v>
+        <v>-0.002197149944957089</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001034268953398956</v>
+        <v>0.001013482965448684</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0004239098171708172</v>
+        <v>-0.0008272415747562518</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001023198683521415</v>
+        <v>-0.002551684872414148</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.000406401329760478</v>
+        <v>-0.0009328593811675889</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001864559484208042</v>
+        <v>-2.097131642384565e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007914807313644744</v>
+        <v>0.001747355647022941</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001772402925326527</v>
+        <v>5.334233449200701e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008137934526908863</v>
+        <v>0.001680845997752528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001619105770770146</v>
+        <v>0.001630750212794618</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.001064341967811921</v>
+        <v>0.00284447859390502</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0006722226974447854</v>
+        <v>-0.001215174866627133</v>
       </c>
       <c r="I7" t="n">
-        <v>6.142549731522618e-05</v>
+        <v>-1.542733724160805e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001024117382448314</v>
+        <v>0.0007634664274186575</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01054142351318309</v>
+        <v>0.008841910208034664</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01032932594834455</v>
+        <v>0.0190254515976621</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.000862038541187926</v>
+        <v>0.000182811887437162</v>
       </c>
       <c r="N7" t="n">
-        <v>9.553264505529602e-06</v>
+        <v>0.000730158237648848</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0003459657549526651</v>
+        <v>8.935575749931534e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006185008366993738</v>
+        <v>0.006423213469537736</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0030207066629302</v>
+        <v>0.003870174213747313</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0009253078798668046</v>
+        <v>-0.001229318477132108</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002505307336884199</v>
+        <v>8.747492257527023e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001309961479217636</v>
+        <v>0.0002833022543447528</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.000702583939244944</v>
+        <v>0.001332382926544867</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.029829919243831e-05</v>
+        <v>0.0001205625970679192</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0006194019586018729</v>
+        <v>-0.001850395861295945</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.002343486870047673</v>
+        <v>-0.0005197567214542009</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004422364654052657</v>
+        <v>0.0007577869625274847</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0004041729586754361</v>
+        <v>0.0008264638241856692</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.755695987012198e-06</v>
+        <v>0.001667096129650841</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002527107435853937</v>
+        <v>0.0002887069276588883</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003345181095649585</v>
+        <v>0.00177498835003948</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.00015220700152207</v>
+        <v>-0.002124544279413115</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.002740829868542055</v>
+        <v>0.0002781819171734645</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001905791009588742</v>
+        <v>-0.0002074688796680601</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0002131844235180646</v>
+        <v>0.000202892700305568</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.961818524399695e-05</v>
+        <v>0.0002469230015021306</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.001221038223263671</v>
+        <v>-0.002171316827101943</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.002697664547720413</v>
+        <v>-0.001534830798603182</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.972651605231968e-05</v>
+        <v>6.327111673523622e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.000134396508013751</v>
+        <v>0.0006827407178204847</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002588311700650658</v>
+        <v>0.002664632327886091</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0006426352022721682</v>
+        <v>-0.0009058435005879162</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.588909531529126e-05</v>
+        <v>-0.000362804766497582</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001307580083199034</v>
+        <v>0.002041280021411118</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.001415183434265566</v>
+        <v>-0.002005617855254427</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.000801526625401222</v>
+        <v>0.001494738902840803</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.001443932583068658</v>
+        <v>-0.0005764722583156635</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0004998295126523722</v>
+        <v>0.0007413906918197599</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0009920557356339899</v>
+        <v>0.0007016378107965793</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0008070284381097969</v>
+        <v>-0.001118698180625233</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0003070718698523656</v>
+        <v>9.451623316060754e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0005674429087966393</v>
+        <v>0.00250442715029296</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.002405073799908774</v>
+        <v>-0.001436813367994511</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.004420969217513509</v>
+        <v>-0.003528242349560767</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0004723054497139833</v>
+        <v>-0.002094290577741897</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0002572211766817656</v>
+        <v>-0.0002869712525419343</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0001906655502215138</v>
+        <v>-0.0001377753820148597</v>
       </c>
       <c r="BE7" t="n">
-        <v>-7.409602845287466e-05</v>
+        <v>4.567388017375773e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0003769797283874277</v>
+        <v>-0.005456945173108352</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.002079236235333365</v>
+        <v>0.00234902796693186</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>6.327111673518627e-05</v>
+        <v>0.0001787165384399658</v>
       </c>
       <c r="BJ7" t="n">
-        <v>7.178322127757153e-05</v>
+        <v>-0.0005166237560508935</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0006322645116215609</v>
+        <v>-0.002296712146805463</v>
       </c>
       <c r="BL7" t="n">
-        <v>-3.123048094941239e-05</v>
+        <v>9.114875879666083e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.002612887430265826</v>
+        <v>0.0002698920307312392</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.003013094176118269</v>
+        <v>-0.002575285463047738</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0007438791493002527</v>
+        <v>0.0003988626887565072</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.000682546320851174</v>
+        <v>0.001410863443398741</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-1.110223024625157e-17</v>
+        <v>0.0002256568367331513</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0006909188163598312</v>
+        <v>0.001298388271985523</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.001132944198123664</v>
+        <v>-0.0007825294123556759</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0001262212464112067</v>
+        <v>-0.0002728791629928396</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.002327010266646434</v>
+        <v>0.001631851052385885</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0003887607021947958</v>
+        <v>0.0005420057530629407</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.0009999769177607199</v>
+        <v>0.003615183299510682</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.496557916791375e-05</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0001379385190451721</v>
+        <v>0.0006404502699676795</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0001049680662660979</v>
+        <v>0.0003765886197747758</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-1.675927449040771e-07</v>
+        <v>0.0004055616496885462</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.002313047543322871</v>
+        <v>-0.0002761781948757036</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>4.684572142411025e-05</v>
+        <v>0.0002373496509400774</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.00069034225653265</v>
+        <v>0.0005826248265824007</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.00137829231345592</v>
+        <v>0.001952612143081639</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001993155616044351</v>
+        <v>-0.0002363165862419636</v>
       </c>
       <c r="CI7" t="n">
-        <v>-7.436048655670713e-05</v>
+        <v>-0.001655730621950535</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0003996157290600156</v>
+        <v>0.003521637631042151</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0002983325683665994</v>
+        <v>0.0009528164255910854</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003471504107121434</v>
+        <v>0.003067873019633285</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002973549827782834</v>
+        <v>0.003284941340735739</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002118537996374453</v>
+        <v>0.005571059663149691</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003632773224197902</v>
+        <v>0.002472681407461386</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003214426700883269</v>
+        <v>0.003968941614957905</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00187140538706046</v>
+        <v>0.0009267676538942116</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002013739729041702</v>
+        <v>6.690454950937784e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002207308334774704</v>
+        <v>0.001649156203097019</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0136881930299162</v>
+        <v>0.01814854401343986</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01878152710967801</v>
+        <v>0.02182428318069406</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0007686015489234449</v>
+        <v>0.001980939737972307</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001694590106714591</v>
+        <v>0.003999966079263462</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007488307509205984</v>
+        <v>0.00441365680851849</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01578361617716126</v>
+        <v>0.01762997069274126</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.007172979316521791</v>
+        <v>0.01039164303254958</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0003573334310934068</v>
+        <v>0.00170772460166837</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0008159372107488183</v>
+        <v>0.001655229702092423</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0009141472579867888</v>
+        <v>0.002127764706675528</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.326966920808017e-06</v>
+        <v>0.002618626149988176</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002129543560680264</v>
+        <v>0.0002002046927572887</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004441853556338729</v>
+        <v>0.002939404405079182</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00384399306199476</v>
+        <v>0.001284234105164952</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.002159897165757247</v>
+        <v>0.002325654705820956</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001103928486333602</v>
+        <v>0.001101092132195924</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009881673732118181</v>
+        <v>0.002528570922252477</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0002964097758908713</v>
+        <v>0.0009624332850108081</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006711187049872003</v>
+        <v>0.00449507883891471</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0007655064044156584</v>
+        <v>-0.0009188893426889083</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001702363471969853</v>
+        <v>0.004404676808982627</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.00182968516135569</v>
+        <v>0.002397413024085682</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0004663383108648333</v>
+        <v>0.0003223804436396027</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0004234861836007798</v>
+        <v>0.0006701797920948577</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.003794980459164879</v>
+        <v>0.002224045282698325</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.001619156238316685</v>
+        <v>-0.0002468373958654624</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0006089665468641675</v>
+        <v>0.0004658122564650952</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0005070255573450921</v>
+        <v>0.0012054567091586</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.005336878762292457</v>
+        <v>0.005083258222290776</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0009639084253564328</v>
+        <v>0.0009881088866287692</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0007745313287087108</v>
+        <v>0.0007307321480817974</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002931901462230122</v>
+        <v>0.003625288250193589</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001250938060548412</v>
+        <v>-0.0002076214256695935</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001338280157816227</v>
+        <v>0.003052789148867688</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00326560593156548</v>
+        <v>0.002136150042965135</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001688363971611536</v>
+        <v>0.005484306474376813</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001536476385868971</v>
+        <v>0.002959513369028216</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002124617688288485</v>
+        <v>0.0002714551957642419</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0007600721969772655</v>
+        <v>0.0007573588215566834</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002266707728399026</v>
+        <v>0.003068122872469889</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001229717161174168</v>
+        <v>0.00578535767644433</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.606069521956245e-05</v>
+        <v>0.002261426607621947</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0003415649803845122</v>
+        <v>0.001259696024041915</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0003077191053452416</v>
+        <v>0.0001984427530442673</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002670388145944641</v>
+        <v>0.0007264263531717747</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>0.0001466309585515718</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0006535592938519186</v>
+        <v>-0.0005866994914741686</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.00139603855769504</v>
+        <v>0.003989943850521808</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0004772673738314331</v>
+        <v>0.0005881818475844125</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0007986931849262774</v>
+        <v>0.002286701924302315</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0008085956118774329</v>
+        <v>0.003185443990118828</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0003949435597368517</v>
+        <v>0.0004028671487169316</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.003886761698595931</v>
+        <v>0.001432341446837468</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0005431567817935328</v>
+        <v>0.0009894959460681808</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.003761037730411504</v>
+        <v>0.005268908668083663</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.002744385431272026</v>
+        <v>0.00338981681226054</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.674613411338462e-05</v>
+        <v>0.0002951951634008326</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001131493358254226</v>
+        <v>0.003854690350778442</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002377500955779252</v>
+        <v>0.001400213939875994</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0008994591418184956</v>
+        <v>0.0007588047336852255</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.00941452108665688</v>
+        <v>0.008470742301476954</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002103134942791155</v>
+        <v>0.003095497033398714</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001262785336948852</v>
+        <v>0.004729781022315777</v>
       </c>
       <c r="BX8" t="n">
-        <v>5.408963196216754e-05</v>
+        <v>0.0001219628713789084</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.451489958543999e-05</v>
+        <v>0.00133961849131769</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0007049004067440828</v>
+        <v>0.0005623408715816458</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>6.150271187700673e-05</v>
+        <v>0.0009131456505732354</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003504309087758326</v>
+        <v>0.0001873828856964382</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0002637508529278909</v>
+        <v>0.0009420640790154117</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002479048642840498</v>
+        <v>0.001595017034084834</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.002515156738502067</v>
+        <v>0.005606281967686023</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002330654736864029</v>
+        <v>0.0004451727065395705</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.00138122213463828</v>
+        <v>0.0006236110650436305</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.003209993726757237</v>
+        <v>0.005470920451204889</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0009382344273939857</v>
+        <v>0.001628511624586146</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007870081199250445</v>
+        <v>0.004042806183115399</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007034865782166044</v>
+        <v>0.008022215365627916</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007245471580262353</v>
+        <v>0.007820398453761545</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009923896499238971</v>
+        <v>0.005857865001486795</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003686087990487496</v>
+        <v>0.007452858425621134</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003638089212274587</v>
+        <v>0.01050583657587556</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002847200253084381</v>
+        <v>0.0008323424494649512</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002800608828006112</v>
+        <v>0.002341434499110839</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0263394193355283</v>
+        <v>0.02925311203319503</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03849583828775266</v>
+        <v>0.02295587781548909</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007089319175515296</v>
+        <v>0.008279668813247432</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008531510107015439</v>
+        <v>0.005737217598097555</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009782275375651683</v>
+        <v>0.009069283377936365</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03881683011705156</v>
+        <v>0.04185384372034168</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01144708423326138</v>
+        <v>0.0179575265459088</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001326751002776971</v>
+        <v>0.005581110088929753</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004555520404935143</v>
+        <v>0.006212841854934659</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003330359797799531</v>
+        <v>0.003122212310437134</v>
       </c>
       <c r="U9" t="n">
-        <v>0.007788347205707491</v>
+        <v>0.005985806849737763</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005933791380387299</v>
+        <v>0.0005053507728894346</v>
       </c>
       <c r="W9" t="n">
-        <v>0.008150563129816213</v>
+        <v>0.01155898043864845</v>
       </c>
       <c r="X9" t="n">
-        <v>0.007031963470319647</v>
+        <v>0.003508771929824584</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003448275862068984</v>
+        <v>0.003606453653906994</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003835616438356193</v>
+        <v>0.002217364147407841</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.005527795128044998</v>
+        <v>0.006423135464231344</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0008892977614229136</v>
+        <v>0.001215174866627144</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.008415058525782993</v>
+        <v>0.007153729071537285</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01119288561790865</v>
+        <v>0.009628948175406294</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.007701674277016768</v>
+        <v>0.01227459664663083</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007255426702349044</v>
+        <v>0.007560898449857656</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006837098692033083</v>
+        <v>0.001393005334914044</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.000547945205479472</v>
+        <v>0.001461187214611859</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00949066751028157</v>
+        <v>0.006959822840873153</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.005219867130654876</v>
+        <v>0.004270800379626715</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.000981266726137331</v>
+        <v>0.001511558980438643</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0009490667510281492</v>
+        <v>0.002186133666458412</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.007807620237351642</v>
+        <v>0.007719076241695688</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.00630389533154917</v>
+        <v>0.001676684593483135</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002269242563630825</v>
+        <v>0.001541197391819793</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.004322678843226823</v>
+        <v>0.004566210045662078</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.004341361879274408</v>
+        <v>0.006868867082961661</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.002594115786143658</v>
+        <v>0.006554923675546309</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.01249219237976262</v>
+        <v>0.002606562404170454</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.007307932542161133</v>
+        <v>0.01999386691199016</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.004809494066208652</v>
+        <v>0.004808604871875999</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003793716656787183</v>
+        <v>0.002087946852261957</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002913216804661189</v>
+        <v>0.002186133666458423</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.003685196752030007</v>
+        <v>0.004434728294815671</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006896551724137901</v>
+        <v>0.01367419738406664</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.002065249925172097</v>
+        <v>0.006325208269052795</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.002406664609688425</v>
+        <v>0.004535637149028137</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001943844492440627</v>
+        <v>0.001357605677260143</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.002653502005553898</v>
+        <v>0.00136032900980706</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0003435352904434752</v>
+        <v>0.0004190362167015849</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01611492816989381</v>
+        <v>0.006109225547670493</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01275267538644468</v>
+        <v>0.007609988109393617</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001758716445541531</v>
+        <v>0.003420096852300292</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.001491628614916307</v>
+        <v>0.005465334166146097</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004458977407847775</v>
+        <v>0.009150530918176091</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001393005334914044</v>
+        <v>0.001391964568174675</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.008115338882282986</v>
+        <v>0.004011107682813974</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.005496564647095592</v>
+        <v>0.00620056944005064</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01311680199875076</v>
+        <v>0.007344632768361603</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003074581430745849</v>
+        <v>0.01498661909009815</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001226617601962643</v>
+        <v>0.0005245294662141852</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.004017172646427513</v>
+        <v>0.01534344335414812</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.008234244946492253</v>
+        <v>0.003172702783597714</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002974547684759332</v>
+        <v>0.004262496166819963</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.02002453235203928</v>
+        <v>0.02063784115302052</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00272397094430995</v>
+        <v>0.008269052761493412</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.004599816007359736</v>
+        <v>0.01836859858938972</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.000151331719128367</v>
+        <v>0.000386559619387461</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0003796267004112508</v>
+        <v>0.00291321680466109</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.003771849126034998</v>
+        <v>0.001575505350772932</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002759889604415866</v>
+        <v>0.001167315175097272</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.006378411530205519</v>
+        <v>0.003835860838537042</v>
       </c>
       <c r="CD9" t="n">
-        <v>9.132420091324533e-05</v>
+        <v>2.993115833582749e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001809260962894865</v>
+        <v>0.001901257283041979</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.004756242568370972</v>
+        <v>0.005055010407374394</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.003360095153137044</v>
+        <v>0.009414290095062849</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.004017172646427513</v>
+        <v>0.003802514566083992</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.006057838660578396</v>
+        <v>0.001882135143474251</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.006333630686886671</v>
+        <v>0.01398344066237347</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002435977514053733</v>
+        <v>0.003172702783597714</v>
       </c>
     </row>
   </sheetData>
